--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2022_arica_y_parinacota.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2022_arica_y_parinacota.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>333740.88</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>216288.23</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>183189.95</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -434,9 +420,6 @@
       </c>
       <c r="B5">
         <v>172897.08</v>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2022_arica_y_parinacota.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2022_arica_y_parinacota.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,34 +391,62 @@
       <c r="B2">
         <v>333740.88</v>
       </c>
+      <c r="C2">
+        <v>289332.72</v>
+      </c>
+      <c r="D2">
+        <v>44408.16000000003</v>
+      </c>
+      <c r="E2">
+        <v>15.34847493225102</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Putre</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B3">
-        <v>216288.23</v>
+        <v>332491.41</v>
+      </c>
+      <c r="C3">
+        <v>288351.78</v>
+      </c>
+      <c r="D3">
+        <v>44139.62999999995</v>
+      </c>
+      <c r="E3">
+        <v>15.30756286644042</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Putre</t>
         </is>
       </c>
       <c r="B4">
-        <v>183189.95</v>
+        <v>216288.23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>183189.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>General Lagos</t>
         </is>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>172897.08</v>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2022_arica_y_parinacota.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2022_arica_y_parinacota.xlsx
@@ -457,7 +457,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -466,20 +466,12 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>333740.88</v>
+          <t>Putre</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -488,28 +480,19 @@
           <t>Camarones</t>
         </is>
       </c>
-      <c r="B3">
-        <v>183189.95</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>General Lagos</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>172897.08</v>
+          <t>Arica</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Putre</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>216288.23</v>
+          <t>General Lagos</t>
+        </is>
       </c>
     </row>
   </sheetData>
